--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -21013,13 +21013,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C56B85EA-BB03-489A-AEA1-AE7770DE40EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA132F6-C3A5-4581-9DC4-43F949638D6E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351065FE-E0C0-41F2-BC27-01B152248610}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86437826-F9C3-4237-A8C9-68D0B0380BCF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9122C637-97AF-42FF-8C9E-E73FCD3E966A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE07EF8-235E-40A6-9554-E2722C875084}"/>
 </file>
--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -22191,13 +22191,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDF8AEE7-6054-4036-A4C1-29AEE296F9BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E09BDDA4-2F32-40F8-B9B7-3E646DB4321E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF527DA8-066E-4BEE-AB22-ECC58B814410}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D71EE7F7-8AC2-474B-9475-399269FA5534}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9C5841E-3977-49C2-9FA8-4F7DD9DEA299}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C9776F-6D62-4920-B36D-B260647C1A01}"/>
 </file>
--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -32297,13 +32297,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60A720EA-C7C5-4DDE-BFC2-39FB21775EAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA135AA9-95D7-4942-8CE6-9C2401F550EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7776E88-2C00-40B4-8D06-C7D53A0F830E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EAFF2BF-15BB-4881-8B38-1375D0744DE0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{308C8321-AF9D-4719-BB13-A7F2EDEE4898}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58B0C922-C4A0-42D6-9581-842CD94AC3FD}"/>
 </file>
--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -33723,13 +33723,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF6B0B40-EB55-43AC-AFF3-02AA24AB0905}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E05C87-7781-47A4-ABAE-69970DC4A812}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B25F745-139B-46B8-957C-C17BCEF1B986}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6DE0410-95E1-48BA-8FD1-69B516FDE9C6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EC37FDA-78AD-493C-A647-AC83C0F904ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8612B727-233B-4BC5-9A11-4D5541C4EE7A}"/>
 </file>
--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -57297,13 +57297,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4181F9A7-2659-4D82-B0F9-3D4D93932E71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BF9A483-1AFE-498B-AC58-B7D3391FDEE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4546A94F-401E-41B4-B3A0-9AEB32536978}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2CF611B-D92A-45FC-BCF4-AC6EDD5BF379}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B01F73-E253-49C9-B068-29F5A74A83DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC63B63-B84E-4025-A407-81BF3218CBD9}"/>
 </file>
--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -57297,13 +57297,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BF9A483-1AFE-498B-AC58-B7D3391FDEE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB32B39-B38F-480C-B9D0-AAECD2CEC31C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2CF611B-D92A-45FC-BCF4-AC6EDD5BF379}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D36FE4C0-82C1-43AB-AD5F-048E31F496EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC63B63-B84E-4025-A407-81BF3218CBD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D66B32-F739-454A-9815-D4A4431B72FC}"/>
 </file>
--- a/Presencas_colectivas.xlsx
+++ b/Presencas_colectivas.xlsx
@@ -76124,13 +76124,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B0EC1B1-3A5D-4020-AD7B-AC0E92A4A37C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5D5063D-24C6-4A36-BD97-0C1B1F60D132}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{913B98B8-9BE1-404A-BF1F-2E6693262D68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{576C2058-3489-4719-A7B1-88DAE9DABBC0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38C10FC5-264D-41B4-B96A-81CC2E9135A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72417AC1-DA4B-416A-8427-9F632F58BCAD}"/>
 </file>